--- a/output/test.xlsx
+++ b/output/test.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>92.30769230769231</v>
+        <v>83.00653594771242</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -505,25 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>84.61538461538461</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>91.66666666666666</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.692307692307693</v>
+        <v>7.189542483660134</v>
       </c>
     </row>
     <row r="4">
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>92.30769230769231</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
